--- a/Tennis/postplanner-imports/tfr-postplanner-2026-04-18.xlsx
+++ b/Tennis/postplanner-imports/tfr-postplanner-2026-04-18.xlsx
@@ -478,7 +478,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>04/18/2026  12:56</t>
+          <t>04/18/2026  08:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>04/18/2026  14:13</t>
+          <t>04/18/2026  10:30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -508,7 +508,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>04/18/2026  15:30</t>
+          <t>04/18/2026  12:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -522,7 +522,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>04/18/2026  16:47</t>
+          <t>04/18/2026  15:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -536,7 +536,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>04/18/2026  18:04</t>
+          <t>04/18/2026  18:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>04/18/2026  19:21</t>
+          <t>04/18/2026  21:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -564,7 +564,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>04/18/2026  20:38</t>
+          <t>04/18/2026  21:05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
